--- a/artfynd/A 20570-2025 artfynd.xlsx
+++ b/artfynd/A 20570-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69886062</v>
+        <v>69885662</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>779733.0763173094</v>
+        <v>779738</v>
       </c>
       <c r="R2" t="n">
-        <v>7511811.893838421</v>
+        <v>7511761</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2017-07-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-07-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,12 +780,7 @@
         <v>69885701</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779739.0566309959</v>
+        <v>779739</v>
       </c>
       <c r="R3" t="n">
-        <v>7511817.144477832</v>
+        <v>7511817</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2017-07-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-07-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -912,12 +882,7 @@
         <v>69885446</v>
       </c>
       <c r="B4" t="n">
-        <v>98493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779974.2395227859</v>
+        <v>779974</v>
       </c>
       <c r="R4" t="n">
-        <v>7511610.852124205</v>
+        <v>7511611</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,19 +947,9 @@
           <t>2017-07-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-07-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69885662</v>
+        <v>69885447</v>
       </c>
       <c r="B5" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>779738.1306418807</v>
+        <v>779457</v>
       </c>
       <c r="R5" t="n">
-        <v>7511760.927341388</v>
+        <v>7511944</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,19 +1049,9 @@
           <t>2017-07-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-07-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69885447</v>
+        <v>69886061</v>
       </c>
       <c r="B6" t="n">
-        <v>98493</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,13 +1118,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>779456.9962790355</v>
+        <v>779951</v>
       </c>
       <c r="R6" t="n">
-        <v>7511943.873455559</v>
+        <v>7511596</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,19 +1151,9 @@
           <t>2017-07-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1260,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69885015</v>
+        <v>69886062</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,13 +1220,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>779966.8941227456</v>
+        <v>779733</v>
       </c>
       <c r="R7" t="n">
-        <v>7511621.98417192</v>
+        <v>7511812</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,19 +1253,9 @@
           <t>2017-07-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-07-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1377,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69886061</v>
+        <v>69885015</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,13 +1322,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779951.190025697</v>
+        <v>779967</v>
       </c>
       <c r="R8" t="n">
-        <v>7511596.089528579</v>
+        <v>7511622</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,19 +1355,9 @@
           <t>2017-07-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-07-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 20570-2025 artfynd.xlsx
+++ b/artfynd/A 20570-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69885662</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69885701</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69885446</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69885447</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69886061</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69886062</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,8 +1421,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69885015</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>